--- a/Estoque Almox/result.xlsx
+++ b/Estoque Almox/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Qtd Pedido</t>
+          <t>somaComponente</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Qtd Material carteira</t>
+          <t>somaMaterial</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>grupo_concatenado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mediaMateriaPrima</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>media_peca</t>
         </is>
       </c>
     </row>
@@ -493,6 +508,9 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -517,6 +535,9 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -541,6 +562,9 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -565,6 +589,9 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -589,6 +616,9 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -613,6 +643,9 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -637,6 +670,9 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -661,6 +697,9 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -685,6 +724,9 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -709,6 +751,9 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -733,6 +778,9 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -757,6 +805,9 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -781,6 +832,9 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -805,6 +859,9 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -837,6 +894,17 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>61113</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -869,6 +937,17 @@
       <c r="H17" t="n">
         <v>0</v>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>63976</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -901,6 +980,17 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>65306</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -933,6 +1023,17 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>65245</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -965,6 +1066,17 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>65305</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -989,6 +1101,9 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1013,6 +1128,9 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1037,6 +1155,9 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1061,6 +1182,9 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1085,6 +1209,9 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1109,6 +1236,9 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1133,6 +1263,9 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1157,6 +1290,9 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1181,6 +1317,9 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1205,6 +1344,9 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1229,6 +1371,9 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1253,6 +1398,9 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1277,6 +1425,9 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1301,6 +1452,9 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1325,6 +1479,9 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1349,6 +1506,9 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1373,6 +1533,9 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1397,6 +1560,9 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1421,6 +1587,9 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1445,6 +1614,9 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1469,6 +1641,9 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1501,6 +1676,17 @@
       <c r="H42" t="n">
         <v>0</v>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>66148</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1533,6 +1719,17 @@
       <c r="H43" t="n">
         <v>0</v>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>66149</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>334</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1560,10 +1757,21 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.7272</v>
+        <v>202</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>62128</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.4212</v>
       </c>
     </row>
     <row r="45">
@@ -1592,10 +1800,21 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.1332</v>
+        <v>74</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>62139</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.0018</v>
       </c>
     </row>
     <row r="46">
@@ -1621,6 +1840,17 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>63034</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.0013</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1645,6 +1875,9 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1669,6 +1902,9 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1696,10 +1932,21 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>800</v>
+        <v>736</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="50">
@@ -1732,6 +1979,17 @@
       </c>
       <c r="H50" t="n">
         <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>71541</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/Estoque Almox/result.xlsx
+++ b/Estoque Almox/result.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>somaMaterial</t>
+          <t>somaPeso</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1607</v>
+        <v>1093</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>423</v>
+        <v>356</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1098,9 +1098,17 @@
           <t>22348</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>22348</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>17.235</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1125,9 +1133,17 @@
           <t>22446</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>22446</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.996</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1152,9 +1168,17 @@
           <t>22606</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>22606</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>13.398</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1179,9 +1203,17 @@
           <t>22678</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>22678</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15.73</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1206,9 +1238,17 @@
           <t>22704</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>22704</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7.9335</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1233,9 +1273,17 @@
           <t>22838</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>22838</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>30.395</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1260,9 +1308,17 @@
           <t>22863</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>22863</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>21.081</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1287,9 +1343,17 @@
           <t>22912</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>22912</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>31.6192</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1314,9 +1378,17 @@
           <t>22961</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>22961</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>18.281</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1341,9 +1413,17 @@
           <t>23039</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>23039</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>173.54</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1368,9 +1448,17 @@
           <t>23036</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>23036</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10.68</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1671,7 +1759,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1714,7 +1802,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>441</v>
+        <v>313</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1757,7 +1845,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>202</v>
+        <v>0.9468</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1800,7 +1888,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>74</v>
+        <v>0.216</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1932,7 +2020,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>736</v>
+        <v>413</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1975,7 +2063,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>288</v>
+        <v>223</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>

--- a/Estoque Almox/result.xlsx
+++ b/Estoque Almox/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,32 +456,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>grupoConcatenado</t>
+          <t>Qtd Pedido</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>somaComponente</t>
+          <t>mediaMateriaPrima</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>somaPeso</t>
+          <t>media_peca</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>grupo_concatenado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>mediaMateriaPrima</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>media_peca</t>
+          <t>soma_material_carteira</t>
         </is>
       </c>
     </row>
@@ -509,8 +499,6 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -536,8 +524,6 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -563,8 +549,6 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -590,8 +574,6 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -617,8 +599,6 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -644,8 +624,6 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -671,8 +649,6 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -698,8 +674,6 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -725,8 +699,6 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -752,8 +724,6 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -779,8 +749,6 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -806,8 +774,6 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -833,8 +799,6 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -860,8 +824,6 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -883,28 +845,16 @@
           <t>61113</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>61113</t>
-        </is>
+      <c r="F16" t="n">
+        <v>1093</v>
       </c>
       <c r="G16" t="n">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>61113</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
         <v>159</v>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -926,28 +876,16 @@
           <t>63976</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>63976</t>
-        </is>
+      <c r="F17" t="n">
+        <v>574</v>
       </c>
       <c r="G17" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>63976</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
         <v>140</v>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -969,28 +907,16 @@
           <t>65306</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>65306</t>
-        </is>
+      <c r="F18" t="n">
+        <v>356</v>
       </c>
       <c r="G18" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>65306</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
         <v>38</v>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1012,28 +938,16 @@
           <t>65245</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>65245</t>
-        </is>
+      <c r="F19" t="n">
+        <v>167</v>
       </c>
       <c r="G19" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>65245</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
         <v>49</v>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1055,28 +969,16 @@
           <t>65305</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>65305</t>
-        </is>
+      <c r="F20" t="n">
+        <v>185</v>
       </c>
       <c r="G20" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>65305</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
         <v>12</v>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1098,20 +1000,14 @@
           <t>22348</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>22348</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>17.235</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>7.488</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1133,20 +1029,14 @@
           <t>22446</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>22446</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.996</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>24.246</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1168,20 +1058,14 @@
           <t>22606</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>22606</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>13.398</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>35.195</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1203,20 +1087,14 @@
           <t>22678</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>22678</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>15.73</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>8.470000000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1238,20 +1116,14 @@
           <t>22704</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>22704</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7.9335</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>6.4805</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1273,20 +1145,14 @@
           <t>22838</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>22838</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>30.395</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>23.114</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1308,20 +1174,14 @@
           <t>22863</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>22863</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>21.081</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>15.248</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1343,20 +1203,14 @@
           <t>22912</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>22912</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>31.6192</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>15.17</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1378,20 +1232,14 @@
           <t>22961</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>22961</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>18.281</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>20.741</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1413,20 +1261,14 @@
           <t>23039</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>23039</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>173.54</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>40.19</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1448,20 +1290,14 @@
           <t>23036</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>23036</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0.8999999999999999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1487,8 +1323,6 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1514,8 +1348,6 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1541,8 +1373,6 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1568,8 +1398,6 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1595,8 +1423,6 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1622,8 +1448,6 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1649,8 +1473,6 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1676,8 +1498,6 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1703,8 +1523,6 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1730,8 +1548,6 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1753,28 +1569,16 @@
           <t>66148</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>66148</t>
-        </is>
+      <c r="F42" t="n">
+        <v>46</v>
       </c>
       <c r="G42" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>66148</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
         <v>53</v>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1796,28 +1600,16 @@
           <t>66149</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>66149</t>
-        </is>
+      <c r="F43" t="n">
+        <v>313</v>
       </c>
       <c r="G43" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>66149</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
         <v>334</v>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1839,28 +1631,16 @@
           <t>62128</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>62128</t>
-        </is>
+      <c r="F44" t="n">
+        <v>0.9468</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9468</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>62128</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
         <v>0.4212</v>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1882,27 +1662,17 @@
           <t>62139</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>62139</t>
-        </is>
+      <c r="F45" t="n">
+        <v>0.216</v>
       </c>
       <c r="G45" t="n">
-        <v>0.216</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>62139</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0.0018</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1926,19 +1696,13 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>63034</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
         <v>0.0013</v>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1964,8 +1728,6 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1991,8 +1753,6 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2014,28 +1774,16 @@
           <t>7452</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
+      <c r="F49" t="n">
+        <v>413</v>
       </c>
       <c r="G49" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
         <v>95</v>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2057,28 +1805,16 @@
           <t>71541</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>71541</t>
-        </is>
+      <c r="F50" t="n">
+        <v>223</v>
       </c>
       <c r="G50" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>71541</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>263</v>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Estoque Almox/result.xlsx
+++ b/Estoque Almox/result.xlsx
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1093</v>
+        <v>1248</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>7.488</v>
+        <v>20.658</v>
       </c>
     </row>
     <row r="22">
@@ -1035,7 +1035,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>24.246</v>
+        <v>24.672</v>
       </c>
     </row>
     <row r="23">
@@ -1064,7 +1064,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>35.195</v>
+        <v>75.73400000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1093,7 +1093,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>8.470000000000001</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="25">
@@ -1122,7 +1122,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>6.4805</v>
+        <v>5.2639</v>
       </c>
     </row>
     <row r="26">
@@ -1151,7 +1151,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>23.114</v>
+        <v>37.996</v>
       </c>
     </row>
     <row r="27">
@@ -1180,7 +1180,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>15.248</v>
+        <v>32.747</v>
       </c>
     </row>
     <row r="28">
@@ -1209,7 +1209,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>15.17</v>
+        <v>66.3502</v>
       </c>
     </row>
     <row r="29">
@@ -1238,7 +1238,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>20.741</v>
+        <v>16.081</v>
       </c>
     </row>
     <row r="30">
@@ -1267,7 +1267,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>40.19</v>
+        <v>186.767</v>
       </c>
     </row>
     <row r="31">
@@ -1296,7 +1296,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.8999999999999999</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="32">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.9468</v>
+        <v>1.2564</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.216</v>
+        <v>0.2232</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>413</v>
+        <v>622</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>223</v>
+        <v>361</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
